--- a/room_list.xlsx
+++ b/room_list.xlsx
@@ -434,19 +434,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,20 +524,30 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>Check In</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Check Out</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Rooms</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
@@ -547,12 +559,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Emil Maltha</t>
+          <t>BORDEI</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t xml:space="preserve"> SILVIU DUMITRU</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -562,30 +574,38 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Captain</t>
+          <t>Financial Officer</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Single M</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -597,45 +617,53 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Emil Maltha</t>
+          <t>SCHMIDT</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t xml:space="preserve"> FRANZISKA</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Captain</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Single F</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -647,12 +675,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Emil Maltha</t>
+          <t>HANSEN-LINDSTROM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Zhou</t>
+          <t xml:space="preserve"> ULF-PETER MAGNUS</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -662,7 +690,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -672,20 +700,28 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Single M</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -697,12 +733,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>MASILI</t>
+          <t>GULINO</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ANGELO</t>
+          <t xml:space="preserve"> SIMONE</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -717,12 +753,12 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1st Hotel Engineer</t>
+          <t>Chief Engineer</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -732,10 +768,18 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
           <t>Single M</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -747,12 +791,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AGUSTIN</t>
+          <t>BORDEI</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GARRY</t>
+          <t xml:space="preserve"> SILVIU DUMITRU</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -762,17 +806,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>2nd Cook</t>
+          <t>Financial Officer</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -782,10 +826,18 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Single M</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>E</t>
         </is>
@@ -797,12 +849,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CASTILLON</t>
+          <t>Emil Maltha</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JOLLY PANTORILLA</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -812,32 +864,40 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>Captain</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="K12" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
     </row>
@@ -847,12 +907,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>LAURENTE</t>
+          <t>Emil Maltha</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> REYMARK</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -862,32 +922,40 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>Captain</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="K13" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
         </is>
       </c>
     </row>
@@ -897,12 +965,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>MACAPOBRE</t>
+          <t>Emil Maltha</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> HOMBRE</t>
+          <t>Zhou</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -912,32 +980,40 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>Captain</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="K14" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
     </row>
@@ -947,12 +1023,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>GROMIO</t>
+          <t>GAY-YA</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KIMBERLY PANUGAO</t>
+          <t xml:space="preserve"> FELICIANA</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -967,27 +1043,35 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Bar Waiter/Waitress</t>
+          <t>Desktop Publisher</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
           <t>Doble F</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>G</t>
+      <c r="K15" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -997,32 +1081,32 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>OWIYO</t>
+          <t>GAY-YA</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ERICK ODONGO</t>
+          <t xml:space="preserve"> FELICIANA</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Bartender</t>
+          <t>Desktop Publisher</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1032,12 +1116,20 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Doble F</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>J</t>
         </is>
       </c>
     </row>
@@ -1047,17 +1139,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>GROMIO</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ORLANDO</t>
+          <t xml:space="preserve"> KIMBERLY PANUGAO</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1067,27 +1159,35 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Bar Waiter/Waitress</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Doble F</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -1097,47 +1197,55 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>BENTHOTA DEVAGE</t>
+          <t>NUNEZ</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> UDARA MADUSAKA</t>
+          <t xml:space="preserve"> SHELLA GADUGDUG</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Junior Nurse</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Doble F</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>K</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1255,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>MASILI</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TIMOTEO JR. BARNES</t>
+          <t xml:space="preserve"> ANGELO</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1162,32 +1270,40 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Carpenter</t>
+          <t>1st Hotel Engineer</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Single M</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1313,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>BARLAAN</t>
+          <t>OWIYO</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARLON</t>
+          <t xml:space="preserve"> ERICK ODONGO</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1212,32 +1328,40 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Chef De Partie</t>
+          <t>Bartender</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>J</t>
+      <c r="K20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -1247,17 +1371,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>GAY-YA</t>
+          <t>AGUSTIN</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FELICIANA</t>
+          <t xml:space="preserve"> GARRY</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1267,27 +1391,35 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Desktop Publisher</t>
+          <t>2nd Cook</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1429,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>BORDEI</t>
+          <t>AREVALO</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SILVIU DUMITRU</t>
+          <t xml:space="preserve"> TIMOTEO JR. BARNES</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1312,32 +1444,40 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Financial Officer</t>
+          <t>Carpenter</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1487,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>BARLAAN</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RUEL</t>
+          <t xml:space="preserve"> MARLON</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1367,27 +1507,35 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Fitter</t>
+          <t>Chef De Partie</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>J</t>
+      <c r="K23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1545,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SAMSON</t>
+          <t>CASTILLON</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAUL ALDRIN </t>
+          <t xml:space="preserve"> JOLLY PANTORILLA</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1417,27 +1565,35 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Galley Utility</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
+      <c r="K24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -1472,22 +1628,30 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
           <t>Single M</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
+      <c r="K25" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -1497,17 +1661,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>NUNEZ</t>
+          <t>LAURENTE</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SHELLA GADUGDUG</t>
+          <t xml:space="preserve"> REYMARK</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1517,27 +1681,35 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Junior Nurse</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1719,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>MAGDADARO</t>
+          <t>MACAPOBRE</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RAFFY</t>
+          <t xml:space="preserve"> HOMBRE</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1567,27 +1739,35 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Oiler</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>L</t>
+      <c r="K27" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1777,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>MAGDADARO</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ALFIE TRISTAN</t>
+          <t xml:space="preserve"> RAFFY</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1617,27 +1797,35 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Pastry Chef</t>
+          <t>Oiler</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="K28" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Q</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1835,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ORFANO</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NICANOR PANERGO</t>
+          <t xml:space="preserve"> RUEL</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1667,27 +1855,35 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Provision Man</t>
+          <t>Fitter</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>O</t>
+      <c r="K29" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1893,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>MASILI</t>
+          <t>ORFANO</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ANGELO</t>
+          <t xml:space="preserve"> NICANOR PANERGO</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1712,32 +1908,40 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>1st Hotel Engineer</t>
+          <t>Provision Man</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1951,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>NYARIKI</t>
+          <t>SAMSON</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARTIN</t>
+          <t xml:space="preserve"> PAUL ALDRIN </t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1762,26 +1966,42 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>2nd Cook</t>
+          <t>Galley Utility</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr"/>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1789,12 +2009,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>NYARIKI</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARTIN</t>
+          <t xml:space="preserve"> ALFIE TRISTAN</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1804,32 +2024,40 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>2nd Cook</t>
+          <t>Pastry Chef</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Q</t>
+      <c r="K32" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -1839,12 +2067,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>AGUSTIN</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GARRY</t>
+          <t xml:space="preserve"> ORLANDO</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1859,27 +2087,35 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>2nd Cook</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Q</t>
+      <c r="K33" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -1889,12 +2125,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CASTILLON</t>
+          <t>BENTHOTA DEVAGE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JOLLY PANTORILLA</t>
+          <t xml:space="preserve"> UDARA MADUSAKA</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1904,32 +2140,40 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="K34" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -1939,47 +2183,55 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>LAURENTE</t>
+          <t xml:space="preserve">KAPOMBE </t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> REYMARK</t>
+          <t xml:space="preserve"> MIREILLE</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>Waiter</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Doble F</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>U</t>
         </is>
       </c>
     </row>
@@ -1989,47 +2241,55 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>MACAPOBRE</t>
+          <t xml:space="preserve">KAPOMBE </t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> HOMBRE</t>
+          <t xml:space="preserve"> MIREILLE</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>Waiter</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Doble F</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>V</t>
         </is>
       </c>
     </row>
@@ -2064,22 +2324,30 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
           <t>Doble F</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="K37" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>V</t>
         </is>
       </c>
     </row>
@@ -2089,41 +2357,57 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ADNYANA</t>
+          <t>NUNEZ</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PUTU WIDYA</t>
+          <t xml:space="preserve"> SHELLA GADUGDUG</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Bartender</t>
+          <t>Junior Nurse</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr"/>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Doble F</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -2131,12 +2415,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ADNYANA</t>
+          <t>DIAZ CASTILLO</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PUTU WIDYA</t>
+          <t xml:space="preserve"> MANUEL</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2146,32 +2430,40 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Bartender</t>
+          <t>Sommelier</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="K39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -2181,12 +2473,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>OWIYO</t>
+          <t>AHMED</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ERICK ODONGO</t>
+          <t xml:space="preserve"> ALTAF</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2196,34 +2488,34 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Bartender</t>
+          <t>Senior Security Guard</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -2231,12 +2523,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>FERNANDES</t>
+          <t>AHMED</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ROYSTON</t>
+          <t xml:space="preserve"> ALTAF</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2251,27 +2543,35 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Senior Security Guard</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Single M</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2581,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KALIM </t>
+          <t>AJIMON</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MAZHAR</t>
+          <t xml:space="preserve"> ANANTHAKRISHNAN</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2301,21 +2601,29 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr"/>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
       <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -2323,12 +2631,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KALIM </t>
+          <t>AJIMON</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MAZHAR</t>
+          <t xml:space="preserve"> ANANTHAKRISHNAN</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2343,27 +2651,35 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>U</t>
+      <c r="K43" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Z</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2689,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>BISHT</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ORLANDO</t>
+          <t xml:space="preserve"> LALIT</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2388,34 +2704,34 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Service Assistant</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -2423,12 +2739,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>BENTHOTA DEVAGE</t>
+          <t>BISHT</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> UDARA MADUSAKA</t>
+          <t xml:space="preserve"> LALIT</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2438,32 +2754,40 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Service Assistant</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="K45" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2797,12 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>HANSEN-LINDSTROM</t>
+          <t>BOGA</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ULF-PETER MAGNUS</t>
+          <t xml:space="preserve"> FREADY HOMI</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2488,32 +2812,40 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Captain</t>
+          <t>Security Guard</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2855,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>BOGA</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TIMOTEO JR. BARNES</t>
+          <t xml:space="preserve"> FREADY HOMI</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2538,32 +2870,40 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Carpenter</t>
+          <t>Security Guard</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="K47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2913,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>BARLAAN</t>
+          <t>FERNANDES</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARLON</t>
+          <t xml:space="preserve"> ROYSTON</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2588,32 +2928,40 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Chef De Partie</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="K48" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2971,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>GULINO</t>
+          <t xml:space="preserve">KALIM </t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SIMONE</t>
+          <t xml:space="preserve"> MAZHAR</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2638,34 +2986,34 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Chief Engineer</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -2673,47 +3021,55 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>GAY-YA</t>
+          <t xml:space="preserve">KALIM </t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FELICIANA</t>
+          <t xml:space="preserve"> MAZHAR</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Desktop Publisher</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>AC</t>
         </is>
       </c>
     </row>
@@ -2723,49 +3079,49 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>SCHMIDT</t>
+          <t>NORONHA</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANZISKA</t>
+          <t xml:space="preserve"> BONIFACIO JOAO</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>Single F</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -2773,12 +3129,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>BOCCIA</t>
+          <t>NORONHA</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ANTONIO</t>
+          <t xml:space="preserve"> BONIFACIO JOAO</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2788,32 +3144,40 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Executive Sous Chef</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>AD</t>
         </is>
       </c>
     </row>
@@ -2823,12 +3187,12 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>BOCCIA</t>
+          <t>SAHA</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ANTONIO</t>
+          <t xml:space="preserve"> SOUVIK</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2838,34 +3202,34 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Executive Sous Chef</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -2873,12 +3237,12 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>BORDEI</t>
+          <t>SAHA</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SILVIU DUMITRU</t>
+          <t xml:space="preserve"> SOUVIK</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2888,32 +3252,40 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Financial Officer</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>AE</t>
         </is>
       </c>
     </row>
@@ -2923,12 +3295,12 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>VELANKOVIL RAJU</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RUEL</t>
+          <t xml:space="preserve"> RENJITH MON</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2938,34 +3310,34 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Fitter</t>
+          <t>Galley Utility</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -2998,16 +3370,32 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr"/>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>AF</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -3015,12 +3403,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>VELANKOVIL RAJU</t>
+          <t>ADNYANA</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RENJITH MON</t>
+          <t xml:space="preserve"> PUTU WIDYA</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3030,34 +3418,34 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Galley Utility</t>
+          <t>Bartender</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -3065,12 +3453,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>SAMSON</t>
+          <t>ADNYANA</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAUL ALDRIN </t>
+          <t xml:space="preserve"> PUTU WIDYA</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3080,32 +3468,40 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Galley Utility</t>
+          <t>Bartender</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>AE</t>
+      <c r="K58" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>AG</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3511,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>HULLANA</t>
+          <t>BOCCIA</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RAYMUND GARRIDO</t>
+          <t xml:space="preserve"> ANTONIO</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3130,32 +3526,40 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>IT/Communications Officer</t>
+          <t>Executive Sous Chef</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
           <t>Single M</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>AF</t>
+      <c r="K59" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>AH</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3569,55 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>NUNEZ</t>
+          <t>BOCCIA</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SHELLA GADUGDUG</t>
+          <t xml:space="preserve"> ANTONIO</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Junior Nurse</t>
+          <t>Executive Sous Chef</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Single M</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>AI</t>
         </is>
       </c>
     </row>
@@ -3215,12 +3627,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>MAGDADARO</t>
+          <t>MASILI</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RAFFY</t>
+          <t xml:space="preserve"> ANGELO</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3230,32 +3642,40 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Oiler</t>
+          <t>1st Hotel Engineer</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>AG</t>
+          <t>Single M</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>AJ</t>
         </is>
       </c>
     </row>
@@ -3265,12 +3685,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>NYARIKI</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ALFIE TRISTAN</t>
+          <t xml:space="preserve"> MARTIN</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3280,34 +3700,34 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Pastry Chef</t>
+          <t>2nd Cook</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
-      </c>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -3315,12 +3735,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>ORFANO</t>
+          <t>NYARIKI</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NICANOR PANERGO</t>
+          <t xml:space="preserve"> MARTIN</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3330,32 +3750,40 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Provision Man</t>
+          <t>2nd Cook</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>AH</t>
+      <c r="K63" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3793,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>BOGA</t>
+          <t>OWIYO</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FREADY HOMI</t>
+          <t xml:space="preserve"> ERICK ODONGO</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3380,32 +3808,40 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Security Guard</t>
+          <t>Bartender</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>AH</t>
+      <c r="K64" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3851,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>BOGA</t>
+          <t>AGUSTIN</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FREADY HOMI</t>
+          <t xml:space="preserve"> GARRY</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3430,32 +3866,40 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Security Guard</t>
+          <t>2nd Cook</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
+      <c r="K65" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3909,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>AHMED</t>
+          <t>AREVALO</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ALTAF</t>
+          <t xml:space="preserve"> TIMOTEO JR. BARNES</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3480,26 +3924,42 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Senior Security Guard</t>
+          <t>Carpenter</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr"/>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -3507,12 +3967,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>AHMED</t>
+          <t>BARLAAN</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ALTAF</t>
+          <t xml:space="preserve"> MARLON</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3522,32 +3982,40 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Senior Security Guard</t>
+          <t>Chef De Partie</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
         </is>
       </c>
     </row>
@@ -3557,12 +4025,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>BISHT</t>
+          <t>CASTILLON</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LALIT</t>
+          <t xml:space="preserve"> JOLLY PANTORILLA</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3572,26 +4040,42 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Service Assistant</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -3599,12 +4083,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>BISHT</t>
+          <t>HULLANA</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LALIT</t>
+          <t xml:space="preserve"> RAYMUND GARRIDO</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3614,32 +4098,40 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Service Assistant</t>
+          <t>IT/Communications Officer</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Single M</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>AN</t>
         </is>
       </c>
     </row>
@@ -3649,12 +4141,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>DIAZ CASTILLO</t>
+          <t>LAURENTE</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MANUEL</t>
+          <t xml:space="preserve"> REYMARK</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3664,32 +4156,40 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Sommelier</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>AK</t>
+      <c r="K70" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>AO</t>
         </is>
       </c>
     </row>
@@ -3699,12 +4199,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>AJIMON</t>
+          <t>MACAPOBRE</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ANANTHAKRISHNAN</t>
+          <t xml:space="preserve"> HOMBRE</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3714,26 +4214,42 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>AO</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -3741,12 +4257,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>AJIMON</t>
+          <t>MAGDADARO</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ANANTHAKRISHNAN</t>
+          <t xml:space="preserve"> RAFFY</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3756,32 +4272,40 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Oiler</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>AK</t>
+      <c r="K72" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>AP</t>
         </is>
       </c>
     </row>
@@ -3791,12 +4315,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>NORONHA</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BONIFACIO JOAO</t>
+          <t xml:space="preserve"> RUEL</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3806,26 +4330,42 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Fitter</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="I73" s="4" t="inlineStr"/>
-      <c r="J73" s="4" t="inlineStr"/>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -3833,12 +4373,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>NORONHA</t>
+          <t>ORFANO</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BONIFACIO JOAO</t>
+          <t xml:space="preserve"> NICANOR PANERGO</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3848,32 +4388,40 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Provision Man</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
+      <c r="K74" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>AQ</t>
         </is>
       </c>
     </row>
@@ -3883,12 +4431,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>SAHA</t>
+          <t>SAMSON</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SOUVIK</t>
+          <t xml:space="preserve"> PAUL ALDRIN </t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3898,26 +4446,42 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Galley Utility</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr"/>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>AQ</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -3925,12 +4489,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>SAHA</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SOUVIK</t>
+          <t xml:space="preserve"> ALFIE TRISTAN</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3940,32 +4504,40 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Pastry Chef</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
           <t>Doble M</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>AL</t>
+      <c r="K76" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -3975,47 +4547,55 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KAPOMBE </t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MIREILLE</t>
+          <t xml:space="preserve"> ORLANDO</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Waiter</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -4025,1237 +4605,57 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">KAPOMBE </t>
+          <t>BENTHOTA DEVAGE</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MIREILLE</t>
+          <t xml:space="preserve"> UDARA MADUSAKA</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Waiter</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>SULZHUK</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> IVAN</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Ukraine</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>2nd Engineer</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H79" s="4" t="inlineStr"/>
-      <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="4" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>ALDAY</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> JEROME CARANDANG</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Able Seaman</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H80" s="4" t="inlineStr"/>
-      <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>FELISILDA</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> DEMETRIO PELIGRO</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>Able Seaman</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H81" s="4" t="inlineStr"/>
-      <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>ISIDORO</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ROVAN</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>Bar Waiter/Waitress</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H82" s="4" t="inlineStr"/>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>KUMARA</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ATHTHANAYAKA SANATH</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>Butler</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>CHARLES</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>CHAMPOUX</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Canadian</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>Captain</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>STEPHEN</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>KAIZER</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Canadian</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Captain</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H85" s="4" t="inlineStr"/>
-      <c r="I85" s="4" t="inlineStr"/>
-      <c r="J85" s="4" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>DOMANIN</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ANDRIY</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>Ukraine</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>Captain</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="4" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Feng</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>lday</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>Captain</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H87" s="4" t="inlineStr"/>
-      <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>NAULAK</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> GINKHUALLIAN</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>Deck Steward</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H88" s="4" t="inlineStr"/>
-      <c r="I88" s="4" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>MIREILLE</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>PAQUETTE</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>Canadian</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>Enginner</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H89" s="4" t="inlineStr"/>
-      <c r="I89" s="4" t="inlineStr"/>
-      <c r="J89" s="4" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>STEPHEN</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>WHEATCROFT</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>Canadian</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Enginner</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H90" s="4" t="inlineStr"/>
-      <c r="I90" s="4" t="inlineStr"/>
-      <c r="J90" s="4" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>OOSTHUYSE</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> JESSICA KAY</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Field Staff</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H91" s="4" t="inlineStr"/>
-      <c r="I91" s="4" t="inlineStr"/>
-      <c r="J91" s="4" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>LUNDSTROEM</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> EVA KARIN TERESIA</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Field Staff</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H92" s="4" t="inlineStr"/>
-      <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>MELLUISH</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> VICTORIA LOUISE</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Field Staff</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H93" s="4" t="inlineStr"/>
-      <c r="I93" s="4" t="inlineStr"/>
-      <c r="J93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>CHEN</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> QI</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Field Staff</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>GRANT</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> HARRY KEITH</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Field Staff</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H95" s="4" t="inlineStr"/>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>BREDENKAMP</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> NICHOLAS</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Field Staff</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H96" s="4" t="inlineStr"/>
-      <c r="I96" s="4" t="inlineStr"/>
-      <c r="J96" s="4" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>THORP</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> MATTHEW</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Field Staff</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H97" s="4" t="inlineStr"/>
-      <c r="I97" s="4" t="inlineStr"/>
-      <c r="J97" s="4" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>KWIDINI</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> NKULULEKO</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Field Staff</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
-      <c r="I98" s="4" t="inlineStr"/>
-      <c r="J98" s="4" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>PERMANA</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> HILMAN JAYA</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>Expedition Program Coordinator</t>
-        </is>
-      </c>
-      <c r="G99" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H99" s="4" t="inlineStr"/>
-      <c r="I99" s="4" t="inlineStr"/>
-      <c r="J99" s="4" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>JEREMY</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>MARSOLAIS</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>Canadian</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H100" s="4" t="inlineStr"/>
-      <c r="I100" s="4" t="inlineStr"/>
-      <c r="J100" s="4" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>ZACHARY</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>COLLINS</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Canadian</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>FO</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H101" s="4" t="inlineStr"/>
-      <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="4" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>RYAN</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>WIENS</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>Canadian</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>FO</t>
-        </is>
-      </c>
-      <c r="G102" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H102" s="4" t="inlineStr"/>
-      <c r="I102" s="4" t="inlineStr"/>
-      <c r="J102" s="4" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>AYDEN</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Canadian</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>FO</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H103" s="4" t="inlineStr"/>
-      <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="4" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>ALLAN</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> GERALDINE TBC</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Guest Relations Manager</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H104" s="4" t="inlineStr"/>
-      <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="4" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>BARNABA</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> COSIMO</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Junior Engineer</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H105" s="4" t="inlineStr"/>
-      <c r="I105" s="4" t="inlineStr"/>
-      <c r="J105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>MAURICE PHILIPPE</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>VAN DE MAELE BELLO</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>Chile</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>Kayak Guide</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="4" t="inlineStr"/>
-      <c r="J106" s="4" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>ARKANI</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ADIN</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>Laundry Man</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>DELA CRUZ</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> LITO</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Ordinary Seaman</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H108" s="4" t="inlineStr"/>
-      <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="4" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>MURTAKOV</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> DMYTRO</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Ukraine</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Safety Officer</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H109" s="4" t="inlineStr"/>
-      <c r="I109" s="4" t="inlineStr"/>
-      <c r="J109" s="4" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Vivi Kristina</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>Bolin</t>
-        </is>
-      </c>
-      <c r="D110" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>Finnish</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>Science &amp; Education CoordinatorNIS</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H110" s="4" t="inlineStr"/>
-      <c r="I110" s="4" t="inlineStr"/>
-      <c r="J110" s="4" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>NACARIO</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ESTER</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>Suite Attendant</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H111" s="4" t="inlineStr"/>
-      <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="4" t="inlineStr"/>
+          <t>Doble M</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/room_list.xlsx
+++ b/room_list.xlsx
@@ -526,22 +526,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -573,10 +573,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Single F</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>SINGLE F</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>SINGLE F</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>BISHT</t>
+          <t>MACAPOBRE</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LALIT</t>
+          <t xml:space="preserve"> HOMBRE</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Service Assistant</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t xml:space="preserve">Doble </t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KALIM </t>
+          <t>BISHT</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MAZHAR</t>
+          <t xml:space="preserve"> LALIT</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Service Assistant</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>SAHA</t>
+          <t xml:space="preserve">KALIM </t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SOUVIK</t>
+          <t xml:space="preserve"> MAZHAR</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>VELANKOVIL RAJU</t>
+          <t>SAHA</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RENJITH MON</t>
+          <t xml:space="preserve"> SOUVIK</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Galley Utility</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>NYARIKI</t>
+          <t>VELANKOVIL RAJU</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARTIN</t>
+          <t xml:space="preserve"> RENJITH MON</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2nd Cook</t>
+          <t>Galley Utility</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>OWIYO</t>
+          <t>NYARIKI</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ERICK ODONGO</t>
+          <t xml:space="preserve"> MARTIN</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Bartender</t>
+          <t>2nd Cook</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>AGUSTIN</t>
+          <t>OWIYO</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GARRY</t>
+          <t xml:space="preserve"> ERICK ODONGO</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>2nd Cook</t>
+          <t>Bartender</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>AREVALO</t>
+          <t>AGUSTIN</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TIMOTEO JR. BARNES</t>
+          <t xml:space="preserve"> GARRY</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Carpenter</t>
+          <t>2nd Cook</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>BARLAAN</t>
+          <t>AREVALO</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARLON</t>
+          <t xml:space="preserve"> TIMOTEO JR. BARNES</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Chef De Partie</t>
+          <t>Carpenter</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>CASTILLON</t>
+          <t>BARLAAN</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JOLLY PANTORILLA</t>
+          <t xml:space="preserve"> MARLON</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>Chef De Partie</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>LAURENTE</t>
+          <t>CASTILLON</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> REYMARK</t>
+          <t xml:space="preserve"> JOLLY PANTORILLA</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>MACAPOBRE</t>
+          <t>LAURENTE</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> HOMBRE</t>
+          <t xml:space="preserve"> REYMARK</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PHANI</t>
+          <t xml:space="preserve"> RODNEY</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>ANUMUKONDA</t>
+          <t>SENO</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -4300,12 +4300,12 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KIRTI KUMAR</t>
+          <t xml:space="preserve"> PHANI</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>JENA</t>
+          <t>ANUMUKONDA</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>Service Assistant</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DEEPAK</t>
+          <t xml:space="preserve"> KIRTI KUMAR</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>KESHTWAL</t>
+          <t>JENA</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Service Assistant</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SAGAR </t>
+          <t xml:space="preserve"> DEEPAK</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNU </t>
+          <t>KESHTWAL</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NANDLAL</t>
+          <t xml:space="preserve"> SAGAR </t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>RAJBHAR</t>
+          <t xml:space="preserve">LNU </t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>Galley Utility</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LAIJU</t>
+          <t xml:space="preserve"> NANDLAL</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>THOMAS</t>
+          <t>RAJBHAR</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Chef De Partie</t>
+          <t>Galley Utility</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> I GUSTI NGURAH BAGUS</t>
+          <t xml:space="preserve"> LAIJU</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>SUADNYA</t>
+          <t>THOMAS</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>Bartender</t>
+          <t>Chef De Partie</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FNU</t>
+          <t xml:space="preserve"> I GUSTI NGURAH BAGUS</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>TEGUH</t>
+          <t>SUADNYA</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Laundry Man</t>
+          <t>Bartender</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ROBIN NICENO</t>
+          <t xml:space="preserve"> FNU</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>ALABASTRO</t>
+          <t>TEGUH</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>Junior Nurse</t>
+          <t>Laundry Man</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DANTE</t>
+          <t xml:space="preserve"> ROBIN NICENO</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>ASEOCHE</t>
+          <t>ALABASTRO</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>2nd Cook</t>
+          <t>Junior Nurse</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JONATHAN</t>
+          <t xml:space="preserve"> DANTE</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>BALANCIO</t>
+          <t>ASEOCHE</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>2nd Cook</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RONNIE GIDOR</t>
+          <t xml:space="preserve"> JONATHAN</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>BALLINAS</t>
+          <t>BALANCIO</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>Fitter</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ERMIE</t>
+          <t xml:space="preserve"> RONNIE GIDOR</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>CARINO</t>
+          <t>BALLINAS</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>Chef De Partie</t>
+          <t>Fitter</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WILLIAM</t>
+          <t xml:space="preserve"> ERMIE</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>DOLLENTAS</t>
+          <t>CARINO</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>Chef De Cuisine</t>
+          <t>Chef De Partie</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JERUH FULAY</t>
+          <t xml:space="preserve"> WILLIAM</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>FLORIDA</t>
+          <t>DOLLENTAS</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>Carpenter</t>
+          <t>Chef De Cuisine</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ERIK MARIONNE MANUIT</t>
+          <t xml:space="preserve"> JERUH FULAY</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>JATULAN</t>
+          <t>FLORIDA</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>Galley Utility</t>
+          <t>Carpenter</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUSTIN HANNS ORTIZO</t>
+          <t xml:space="preserve"> ERIK MARIONNE MANUIT</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>LANIOG</t>
+          <t>JATULAN</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>Desktop Publisher</t>
+          <t>Galley Utility</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> EDUARD FLORES</t>
+          <t xml:space="preserve"> JUSTIN HANNS ORTIZO</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>MARIKIT</t>
+          <t>LANIOG</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Able Seaman</t>
+          <t>Desktop Publisher</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GEM LASKER ARCELO</t>
+          <t xml:space="preserve"> EDUARD FLORES</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>PURIO</t>
+          <t>MARIKIT</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>Provision Man</t>
+          <t>Able Seaman</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RODNEY</t>
+          <t xml:space="preserve"> GEM LASKER ARCELO</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>SENO</t>
+          <t>PURIO</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Provision Man</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Doble F</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -5605,12 +5605,12 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RIZWAN</t>
+          <t xml:space="preserve"> ALCIDES IVAN</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>SHAGUL HAMEED</t>
+          <t>PONTE VARA</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Executive Sous Chef</t>
+          <t>IT/Communications Officer</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ALCIDES IVAN</t>
+          <t xml:space="preserve"> NORBERTO</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>PONTE VARA</t>
+          <t>OXENO</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>IT/Communications Officer</t>
+          <t>Head Bartender</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NORBERTO</t>
+          <t xml:space="preserve"> PHANI</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>OXENO</t>
+          <t>ANUMUKONDA</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>Head Bartender</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Single M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>AW</t>
         </is>
       </c>
     </row>
@@ -5785,12 +5785,12 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PHANI</t>
+          <t xml:space="preserve"> KIRTI KUMAR</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>ANUMUKONDA</t>
+          <t>JENA</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Service Assistant</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>AW</t>
+          <t>BA</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> KIRTI KUMAR</t>
+          <t xml:space="preserve"> DEEPAK</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>JENA</t>
+          <t>KESHTWAL</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Service Assistant</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>BA</t>
         </is>
       </c>
     </row>
@@ -5905,12 +5905,12 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DEEPAK</t>
+          <t xml:space="preserve"> SAGAR </t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>KESHTWAL</t>
+          <t xml:space="preserve">LNU </t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SAGAR </t>
+          <t xml:space="preserve"> RIZWAN</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNU </t>
+          <t>SHAGUL HAMEED</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Executive Sous Chef</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>BB</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>BC</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>BD</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>BE</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BF</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6505,12 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NANDLAL</t>
+          <t xml:space="preserve"> I GUSTI NGURAH BAGUS</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>RAJBHAR</t>
+          <t>SUADNYA</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>Galley Utility</t>
+          <t>Bartender</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> I GUSTI NGURAH BAGUS</t>
+          <t xml:space="preserve"> RODNEY</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>SUADNYA</t>
+          <t>SENO</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>Bartender</t>
+          <t>Suite Attendant</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>BH</t>
+          <t>BG</t>
         </is>
       </c>
     </row>
@@ -6625,12 +6625,12 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ERIK MARIONNE MANUIT</t>
+          <t xml:space="preserve"> NANDLAL</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>JATULAN</t>
+          <t>RAJBHAR</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>India</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JUSTIN HANNS ORTIZO</t>
+          <t xml:space="preserve"> ERIK MARIONNE MANUIT</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>LANIOG</t>
+          <t>JATULAN</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>Desktop Publisher</t>
+          <t>Galley Utility</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>BH</t>
         </is>
       </c>
     </row>
@@ -6745,12 +6745,12 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RODNEY</t>
+          <t xml:space="preserve"> JUSTIN HANNS ORTIZO</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>SENO</t>
+          <t>LANIOG</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>Suite Attendant</t>
+          <t>Desktop Publisher</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Doble M</t>
+          <t>Doble</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
